--- a/survey_templates/040_smartphone_addiction_assessment--survey_templates.xlsx
+++ b/survey_templates/040_smartphone_addiction_assessment--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'not_a_problem'}</t>
+          <t>not_a_problem</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Not a problem'}</t>
+          <t>Not a problem</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'not_a_problem'}</t>
+          <t>not_a_problem</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Not a problem'}</t>
+          <t>Not a problem</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'not_a_problem'}</t>
+          <t>not_a_problem</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Not a problem'}</t>
+          <t>Not a problem</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'not_a_problem'}</t>
+          <t>not_a_problem</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Not a problem'}</t>
+          <t>Not a problem</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'not_a_problem'}</t>
+          <t>not_a_problem</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Not a problem'}</t>
+          <t>Not a problem</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'not_a_problem'}</t>
+          <t>not_a_problem</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Not a problem'}</t>
+          <t>Not a problem</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'not_a_problem'}</t>
+          <t>not_a_problem</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Not a problem'}</t>
+          <t>Not a problem</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'not_a_problem'}</t>
+          <t>not_a_problem</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Not a problem'}</t>
+          <t>Not a problem</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'not_a_problem'}</t>
+          <t>not_a_problem</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Not a problem'}</t>
+          <t>Not a problem</t>
         </is>
       </c>
     </row>
